--- a/research/traditional_assets/database/data/canada/canada_utility_water.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_utility_water.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.259</v>
+        <v>0.234</v>
       </c>
       <c r="G2">
-        <v>-1.410376044568245</v>
+        <v>-2.046107784431137</v>
       </c>
       <c r="H2">
-        <v>-1.416573816155989</v>
+        <v>-2.046107784431137</v>
       </c>
       <c r="I2">
-        <v>-0.4552981144389353</v>
+        <v>-2.067664670658683</v>
       </c>
       <c r="J2">
-        <v>-0.4552981144389353</v>
+        <v>-2.067664670658683</v>
       </c>
       <c r="K2">
-        <v>-17.725</v>
+        <v>-3.743</v>
       </c>
       <c r="L2">
-        <v>-1.234331476323119</v>
+        <v>-2.241317365269461</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,67 +630,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.7290000000000001</v>
+        <v>0.154</v>
       </c>
       <c r="V2">
-        <v>0.0447239263803681</v>
+        <v>0.004621848739495798</v>
+      </c>
+      <c r="W2">
+        <v>0.04399081666564932</v>
       </c>
       <c r="X2">
-        <v>0.04683109441263147</v>
+        <v>0.06813095717256916</v>
+      </c>
+      <c r="Y2">
+        <v>-0.02414014050691984</v>
       </c>
       <c r="Z2">
-        <v>5.469633102864227</v>
-      </c>
-      <c r="AA2">
-        <v>-2.950257448729315</v>
+        <v>0.3200459946339594</v>
       </c>
       <c r="AB2">
-        <v>0.03768811286056106</v>
-      </c>
-      <c r="AC2">
-        <v>-2.987945561589876</v>
+        <v>0.06773430709833218</v>
       </c>
       <c r="AD2">
-        <v>53.06</v>
+        <v>3.578</v>
       </c>
       <c r="AE2">
-        <v>0.480404616715558</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>53.54040461671556</v>
+        <v>3.578</v>
       </c>
       <c r="AG2">
-        <v>52.81140461671556</v>
+        <v>3.424</v>
       </c>
       <c r="AH2">
-        <v>0.7666107450342753</v>
+        <v>0.09697002547563553</v>
       </c>
       <c r="AI2">
-        <v>136.7904269142153</v>
+        <v>-1.677449601500234</v>
       </c>
       <c r="AJ2">
-        <v>0.7641489115957336</v>
+        <v>0.0931852819507947</v>
       </c>
       <c r="AK2">
-        <v>-156.4340249647868</v>
+        <v>-1.497157848710101</v>
       </c>
       <c r="AL2">
-        <v>6.587</v>
+        <v>0.416</v>
       </c>
       <c r="AM2">
-        <v>6.587</v>
+        <v>0.416</v>
       </c>
       <c r="AN2">
-        <v>-10.36530572377418</v>
+        <v>-3.246823956442832</v>
       </c>
       <c r="AO2">
-        <v>-1.053590405343859</v>
+        <v>-8.30048076923077</v>
       </c>
       <c r="AP2">
-        <v>-10.3167424529626</v>
+        <v>-3.107078039927405</v>
       </c>
       <c r="AQ2">
-        <v>-1.053590405343859</v>
+        <v>-8.30048076923077</v>
       </c>
     </row>
     <row r="3">
@@ -701,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Clearford Water Systems Inc. (TSXV:CLI)</t>
+          <t>Prime Drink Group Corp. (CNSX:PRME)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -709,26 +709,8 @@
           <t>Utility (Water)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.308</v>
-      </c>
-      <c r="G3">
-        <v>-0.1436842105263158</v>
-      </c>
-      <c r="H3">
-        <v>-0.1503759398496241</v>
-      </c>
-      <c r="I3">
-        <v>-0.1736842105263158</v>
-      </c>
-      <c r="J3">
-        <v>-0.1736842105263158</v>
-      </c>
       <c r="K3">
-        <v>-5.02</v>
-      </c>
-      <c r="L3">
-        <v>-0.3774436090225564</v>
+        <v>-0.489</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +734,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.153</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>0.09503105590062111</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>0.1360433604336043</v>
+        <v>-0.09209039548022599</v>
       </c>
       <c r="X3">
-        <v>0.5008693722738783</v>
+        <v>0.06775208547009129</v>
       </c>
       <c r="Y3">
-        <v>-0.364826011840274</v>
+        <v>-0.1598424809503173</v>
       </c>
       <c r="Z3">
-        <v>7.41360089186175</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>-1.287625418060199</v>
+        <v>-0.09860312243221037</v>
       </c>
       <c r="AB3">
-        <v>0.08188306667035088</v>
+        <v>0.06773354935295173</v>
       </c>
       <c r="AC3">
-        <v>-1.36950848473055</v>
+        <v>-0.1663366717851621</v>
       </c>
       <c r="AD3">
-        <v>49.5</v>
+        <v>0.012</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>49.5</v>
+        <v>0.012</v>
       </c>
       <c r="AG3">
-        <v>49.347</v>
+        <v>0.012</v>
       </c>
       <c r="AH3">
-        <v>0.9684993152025044</v>
+        <v>0.0007836990595611285</v>
       </c>
       <c r="AI3">
-        <v>12.07317073170731</v>
+        <v>0.002590673575129534</v>
       </c>
       <c r="AJ3">
-        <v>0.9684047334026729</v>
+        <v>0.0007836990595611285</v>
       </c>
       <c r="AK3">
-        <v>12.50240689130985</v>
+        <v>0.002590673575129534</v>
       </c>
       <c r="AL3">
-        <v>5.04</v>
+        <v>0.002</v>
       </c>
       <c r="AM3">
-        <v>5.04</v>
+        <v>0.002</v>
       </c>
       <c r="AN3">
-        <v>-29.81927710843374</v>
+        <v>-0.02505219206680585</v>
       </c>
       <c r="AO3">
-        <v>-0.4583333333333333</v>
+        <v>-240</v>
       </c>
       <c r="AP3">
-        <v>-29.72710843373494</v>
+        <v>-0.02505219206680585</v>
       </c>
       <c r="AQ3">
-        <v>-0.4583333333333333</v>
+        <v>-240</v>
       </c>
     </row>
     <row r="4">
@@ -838,25 +820,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.21</v>
+        <v>0.234</v>
       </c>
       <c r="G4">
-        <v>-0.1905660377358491</v>
+        <v>-0.718562874251497</v>
       </c>
       <c r="H4">
-        <v>-0.1905660377358491</v>
+        <v>-0.718562874251497</v>
       </c>
       <c r="I4">
-        <v>-0.8867924528301886</v>
+        <v>-0.3491017964071856</v>
       </c>
       <c r="J4">
-        <v>-0.8867924528301886</v>
+        <v>-0.3491017964071856</v>
       </c>
       <c r="K4">
-        <v>-0.955</v>
+        <v>-0.594</v>
       </c>
       <c r="L4">
-        <v>-0.9009433962264151</v>
+        <v>-0.355688622754491</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -880,73 +862,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.551</v>
+        <v>0.143</v>
       </c>
       <c r="V4">
-        <v>0.07298013245033114</v>
+        <v>0.02604735883424408</v>
       </c>
       <c r="W4">
-        <v>-13.84057971014493</v>
+        <v>-1.022375215146299</v>
       </c>
       <c r="X4">
-        <v>0.03632662538192776</v>
+        <v>0.06850982887504703</v>
       </c>
       <c r="Y4">
-        <v>-13.87690633552685</v>
+        <v>-1.090885044021346</v>
       </c>
       <c r="Z4">
-        <v>3.01994301994302</v>
+        <v>4.771428571428571</v>
       </c>
       <c r="AA4">
-        <v>-2.678062678062678</v>
+        <v>-1.665714285714286</v>
       </c>
       <c r="AB4">
-        <v>0.03594415474680512</v>
+        <v>0.07014253614562227</v>
       </c>
       <c r="AC4">
-        <v>-2.714006832809483</v>
+        <v>-1.735856821859908</v>
       </c>
       <c r="AD4">
-        <v>0.32</v>
+        <v>0.196</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.32</v>
+        <v>0.196</v>
       </c>
       <c r="AG4">
-        <v>-0.231</v>
+        <v>0.05300000000000002</v>
       </c>
       <c r="AH4">
-        <v>0.04066073697585769</v>
+        <v>0.03447062961660218</v>
       </c>
       <c r="AI4">
-        <v>0.3551609322974473</v>
+        <v>0.472289156626506</v>
       </c>
       <c r="AJ4">
-        <v>-0.03156168875529444</v>
+        <v>0.009561609236875341</v>
       </c>
       <c r="AK4">
-        <v>-0.6600000000000003</v>
+        <v>0.1948529411764706</v>
       </c>
       <c r="AL4">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="AM4">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="AN4">
-        <v>-0.320962888665998</v>
+        <v>-0.3146067415730337</v>
       </c>
       <c r="AO4">
-        <v>-62.66666666666666</v>
+        <v>-58.3</v>
       </c>
       <c r="AP4">
-        <v>0.2316950852557673</v>
+        <v>-0.0850722311396469</v>
       </c>
       <c r="AQ4">
-        <v>-62.66666666666666</v>
+        <v>-58.3</v>
       </c>
     </row>
     <row r="5">
@@ -957,7 +939,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rainmaker Worldwide Inc. (OTCPK:RAKR)</t>
+          <t>Quest Water Global, Inc. (OTCPK:QWTR)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -966,7 +948,7 @@
         </is>
       </c>
       <c r="K5">
-        <v>-7.49</v>
+        <v>-1.16</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -990,67 +972,52 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>0.009615384615384616</v>
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0.3101604278074866</v>
       </c>
       <c r="X5">
-        <v>0.05733556344333517</v>
-      </c>
-      <c r="Z5">
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <v>-3.222452219395952</v>
+        <v>0.06773506484371264</v>
+      </c>
+      <c r="Y5">
+        <v>0.242425362963774</v>
       </c>
       <c r="AB5">
-        <v>0.03943207097431699</v>
-      </c>
-      <c r="AC5">
-        <v>-3.261884290370269</v>
+        <v>0.06773506484371264</v>
       </c>
       <c r="AD5">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>0.480404616715558</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>3.720404616715558</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>3.695404616715558</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>0.5886339312638645</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>-0.8071000396708755</v>
+        <v>-0</v>
       </c>
       <c r="AJ5">
-        <v>0.5870003346414812</v>
+        <v>0</v>
       </c>
       <c r="AK5">
-        <v>-0.7973521550648724</v>
+        <v>-0</v>
       </c>
       <c r="AL5">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>1.53</v>
-      </c>
-      <c r="AN5">
-        <v>-4.487534626038782</v>
-      </c>
-      <c r="AO5">
-        <v>-1.274509803921569</v>
-      </c>
-      <c r="AP5">
-        <v>-5.118288942819333</v>
-      </c>
-      <c r="AQ5">
-        <v>-1.274509803921569</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1061,7 +1028,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dominion Water Reserves Corp. (CNSX:DWR)</t>
+          <t>Rainmaker Worldwide Inc. (OTCPK:RAKR)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1070,7 +1037,7 @@
         </is>
       </c>
       <c r="K6">
-        <v>-4.26</v>
+        <v>-1.5</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1094,52 +1061,58 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>0.009734513274336283</v>
+      </c>
+      <c r="W6">
+        <v>0.1800720288115246</v>
       </c>
       <c r="X6">
-        <v>0.03568534419585297</v>
+        <v>0.1324548669609549</v>
+      </c>
+      <c r="Y6">
+        <v>0.04761716185056974</v>
       </c>
       <c r="AB6">
-        <v>0.03568534419585297</v>
+        <v>0.06628688881463977</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>3.359</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.7488888888888889</v>
+      </c>
+      <c r="AI6">
+        <v>-0.5506535947712419</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>0.7482735575852083</v>
+      </c>
+      <c r="AK6">
+        <v>-0.5478714728429294</v>
       </c>
       <c r="AL6">
-        <v>0.002</v>
+        <v>0.404</v>
       </c>
       <c r="AM6">
-        <v>0.002</v>
-      </c>
-      <c r="AN6">
-        <v>-0</v>
+        <v>0.404</v>
       </c>
       <c r="AO6">
-        <v>-870</v>
-      </c>
-      <c r="AP6">
-        <v>-0</v>
+        <v>-2.524752475247525</v>
       </c>
       <c r="AQ6">
-        <v>-870</v>
+        <v>-2.524752475247525</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/canada/canada_utility_water.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_utility_water.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.234</v>
+        <v>0.0342</v>
       </c>
       <c r="G2">
-        <v>-2.046107784431137</v>
+        <v>-1.260232440626579</v>
       </c>
       <c r="H2">
-        <v>-2.046107784431137</v>
+        <v>-1.260232440626579</v>
       </c>
       <c r="I2">
-        <v>-2.067664670658683</v>
+        <v>-1.245073269327943</v>
       </c>
       <c r="J2">
-        <v>-2.067664670658683</v>
+        <v>-1.245073269327943</v>
       </c>
       <c r="K2">
-        <v>-3.743</v>
+        <v>-3.055</v>
       </c>
       <c r="L2">
-        <v>-2.241317365269461</v>
+        <v>-1.543708943911066</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,67 +630,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.154</v>
+        <v>2.35</v>
       </c>
       <c r="V2">
-        <v>0.004621848739495798</v>
+        <v>0.09456740442655934</v>
       </c>
       <c r="W2">
-        <v>0.04399081666564932</v>
+        <v>0.02225457191210617</v>
       </c>
       <c r="X2">
-        <v>0.06813095717256916</v>
+        <v>0.05844415951348705</v>
       </c>
       <c r="Y2">
-        <v>-0.02414014050691984</v>
+        <v>-0.03618958760138088</v>
       </c>
       <c r="Z2">
-        <v>0.3200459946339594</v>
+        <v>0.4035481239804241</v>
       </c>
       <c r="AB2">
-        <v>0.06773430709833218</v>
+        <v>0.05828465007267279</v>
       </c>
       <c r="AD2">
-        <v>3.578</v>
+        <v>4.145</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.578</v>
+        <v>4.145</v>
       </c>
       <c r="AG2">
-        <v>3.424</v>
+        <v>1.795</v>
       </c>
       <c r="AH2">
-        <v>0.09697002547563553</v>
+        <v>0.1429556820141404</v>
       </c>
       <c r="AI2">
-        <v>-1.677449601500234</v>
+        <v>-3.218167701863353</v>
       </c>
       <c r="AJ2">
-        <v>0.0931852819507947</v>
+        <v>0.0673672358791518</v>
       </c>
       <c r="AK2">
-        <v>-1.497157848710101</v>
+        <v>-0.4934029686641012</v>
       </c>
       <c r="AL2">
-        <v>0.416</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AM2">
-        <v>0.416</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AN2">
-        <v>-3.246823956442832</v>
+        <v>-3.480268681780016</v>
       </c>
       <c r="AO2">
-        <v>-8.30048076923077</v>
+        <v>-2.640943193997856</v>
       </c>
       <c r="AP2">
-        <v>-3.107078039927405</v>
+        <v>-1.507136859781696</v>
       </c>
       <c r="AQ2">
-        <v>-8.30048076923077</v>
+        <v>-2.640943193997856</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-0.489</v>
+        <v>-0.695</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -734,73 +734,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="W3">
-        <v>-0.09209039548022599</v>
+        <v>-0.1504329004329004</v>
       </c>
       <c r="X3">
-        <v>0.06775208547009129</v>
+        <v>0.05832309379199274</v>
       </c>
       <c r="Y3">
-        <v>-0.1598424809503173</v>
+        <v>-0.2087559942248932</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.09860312243221037</v>
+        <v>-0.1457253886010363</v>
       </c>
       <c r="AB3">
-        <v>0.06773354935295173</v>
+        <v>0.05832309379199274</v>
       </c>
       <c r="AC3">
-        <v>-0.1663366717851621</v>
+        <v>-0.204048482393029</v>
       </c>
       <c r="AD3">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.012</v>
+        <v>-2.07</v>
       </c>
       <c r="AH3">
-        <v>0.0007836990595611285</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.002590673575129534</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.0007836990595611285</v>
+        <v>-0.2195121951219512</v>
       </c>
       <c r="AK3">
-        <v>0.002590673575129534</v>
+        <v>-0.4509803921568627</v>
       </c>
       <c r="AL3">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AM3">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="AN3">
-        <v>-0.02505219206680585</v>
+        <v>-0</v>
       </c>
       <c r="AO3">
-        <v>-240</v>
+        <v>-675</v>
       </c>
       <c r="AP3">
-        <v>-0.02505219206680585</v>
+        <v>3.071216617210682</v>
       </c>
       <c r="AQ3">
-        <v>-240</v>
+        <v>-675</v>
       </c>
     </row>
     <row r="4">
@@ -820,25 +820,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.234</v>
+        <v>0.0342</v>
       </c>
       <c r="G4">
-        <v>-0.718562874251497</v>
+        <v>-0.3905263157894737</v>
       </c>
       <c r="H4">
-        <v>-0.718562874251497</v>
+        <v>-0.3905263157894737</v>
       </c>
       <c r="I4">
-        <v>-0.3491017964071856</v>
+        <v>-0.04684210526315789</v>
       </c>
       <c r="J4">
-        <v>-0.3491017964071856</v>
+        <v>-0.04684210526315789</v>
       </c>
       <c r="K4">
-        <v>-0.594</v>
+        <v>-0.096</v>
       </c>
       <c r="L4">
-        <v>-0.355688622754491</v>
+        <v>-0.05052631578947369</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -862,73 +862,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.143</v>
+        <v>0.28</v>
       </c>
       <c r="V4">
-        <v>0.02604735883424408</v>
+        <v>0.04973357015985791</v>
       </c>
       <c r="W4">
-        <v>-1.022375215146299</v>
+        <v>-0.4383561643835617</v>
       </c>
       <c r="X4">
-        <v>0.06850982887504703</v>
+        <v>0.05856522523498135</v>
       </c>
       <c r="Y4">
-        <v>-1.090885044021346</v>
+        <v>-0.496921389618543</v>
       </c>
       <c r="Z4">
-        <v>4.771428571428571</v>
+        <v>6.985294117647058</v>
       </c>
       <c r="AA4">
-        <v>-1.665714285714286</v>
+        <v>-0.3272058823529411</v>
       </c>
       <c r="AB4">
-        <v>0.07014253614562227</v>
+        <v>0.05824620635335284</v>
       </c>
       <c r="AC4">
-        <v>-1.735856821859908</v>
+        <v>-0.385452088706294</v>
       </c>
       <c r="AD4">
-        <v>0.196</v>
+        <v>0.095</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.196</v>
+        <v>0.095</v>
       </c>
       <c r="AG4">
-        <v>0.05300000000000002</v>
+        <v>-0.185</v>
       </c>
       <c r="AH4">
-        <v>0.03447062961660218</v>
+        <v>0.0165938864628821</v>
       </c>
       <c r="AI4">
-        <v>0.472289156626506</v>
+        <v>0.2950310559006211</v>
       </c>
       <c r="AJ4">
-        <v>0.009561609236875341</v>
+        <v>-0.0339761248852158</v>
       </c>
       <c r="AK4">
-        <v>0.1948529411764706</v>
+        <v>-4.404761904761907</v>
       </c>
       <c r="AL4">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="AM4">
-        <v>0.01</v>
+        <v>0.007</v>
       </c>
       <c r="AN4">
-        <v>-0.3146067415730337</v>
+        <v>-0.6934306569343065</v>
       </c>
       <c r="AO4">
-        <v>-58.3</v>
+        <v>-12.71428571428571</v>
       </c>
       <c r="AP4">
-        <v>-0.0850722311396469</v>
+        <v>1.35036496350365</v>
       </c>
       <c r="AQ4">
-        <v>-58.3</v>
+        <v>-12.71428571428571</v>
       </c>
     </row>
     <row r="5">
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="K5">
-        <v>-1.16</v>
+        <v>-0.414</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -978,16 +978,16 @@
         <v>0</v>
       </c>
       <c r="W5">
-        <v>0.3101604278074866</v>
+        <v>0.390566037735849</v>
       </c>
       <c r="X5">
-        <v>0.06773506484371264</v>
+        <v>0.05832309379199274</v>
       </c>
       <c r="Y5">
-        <v>0.242425362963774</v>
+        <v>0.3322429439438563</v>
       </c>
       <c r="AB5">
-        <v>0.06773506484371264</v>
+        <v>0.05832309379199274</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1018,6 +1018,12 @@
       </c>
       <c r="AM5">
         <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>-0</v>
+      </c>
+      <c r="AP5">
+        <v>-0</v>
       </c>
     </row>
     <row r="6">
@@ -1036,8 +1042,23 @@
           <t>Utility (Water)</t>
         </is>
       </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>-16.70886075949367</v>
+      </c>
+      <c r="J6">
+        <v>-16.70886075949367</v>
+      </c>
       <c r="K6">
-        <v>-1.5</v>
+        <v>-1.85</v>
+      </c>
+      <c r="L6">
+        <v>-23.41772151898734</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1061,58 +1082,58 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>0.009734513274336283</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>0.1800720288115246</v>
+        <v>0.1949420442571128</v>
       </c>
       <c r="X6">
-        <v>0.1324548669609549</v>
+        <v>0.1102118165110234</v>
       </c>
       <c r="Y6">
-        <v>0.04761716185056974</v>
+        <v>0.08473022774608932</v>
       </c>
       <c r="AB6">
-        <v>0.06628688881463977</v>
+        <v>0.05469338520161437</v>
       </c>
       <c r="AD6">
-        <v>3.37</v>
+        <v>4.05</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>3.37</v>
+        <v>4.05</v>
       </c>
       <c r="AG6">
-        <v>3.359</v>
+        <v>4.05</v>
       </c>
       <c r="AH6">
-        <v>0.7488888888888889</v>
+        <v>0.7833655705996131</v>
       </c>
       <c r="AI6">
-        <v>-0.5506535947712419</v>
+        <v>-0.6183206106870229</v>
       </c>
       <c r="AJ6">
-        <v>0.7482735575852083</v>
+        <v>0.7833655705996131</v>
       </c>
       <c r="AK6">
-        <v>-0.5478714728429294</v>
+        <v>-0.6183206106870229</v>
       </c>
       <c r="AL6">
-        <v>0.404</v>
+        <v>0.925</v>
       </c>
       <c r="AM6">
-        <v>0.404</v>
+        <v>0.925</v>
       </c>
       <c r="AO6">
-        <v>-2.524752475247525</v>
+        <v>-1.427027027027027</v>
       </c>
       <c r="AQ6">
-        <v>-2.524752475247525</v>
+        <v>-1.427027027027027</v>
       </c>
     </row>
   </sheetData>
